--- a/src/attributions/attributions_saliency_traj_80.xlsx
+++ b/src/attributions/attributions_saliency_traj_80.xlsx
@@ -999,1140 +999,1140 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7.604923666804098e-06</v>
+        <v>0.7607084512710571</v>
       </c>
       <c r="B2" t="n">
-        <v>6.532478437293321e-06</v>
+        <v>0.02573119103908539</v>
       </c>
       <c r="C2" t="n">
-        <v>2.288133509864565e-05</v>
+        <v>0.4362431764602661</v>
       </c>
       <c r="D2" t="n">
-        <v>7.889171683927998e-06</v>
+        <v>0.3785587251186371</v>
       </c>
       <c r="E2" t="n">
-        <v>1.742133827065118e-05</v>
+        <v>0.2273183166980743</v>
       </c>
       <c r="F2" t="n">
-        <v>3.192738176949206e-06</v>
+        <v>0.4241982996463776</v>
       </c>
       <c r="G2" t="n">
-        <v>6.99416887073312e-06</v>
+        <v>0.3291258215904236</v>
       </c>
       <c r="H2" t="n">
-        <v>8.735686606087256e-06</v>
+        <v>0.1488499045372009</v>
       </c>
       <c r="I2" t="n">
-        <v>1.482144944020547e-05</v>
+        <v>0.2715006768703461</v>
       </c>
       <c r="J2" t="n">
-        <v>9.170158591587096e-06</v>
+        <v>0.7331050634384155</v>
       </c>
       <c r="K2" t="n">
-        <v>3.433882739045657e-06</v>
+        <v>0.3459924161434174</v>
       </c>
       <c r="L2" t="n">
-        <v>2.771160325210076e-05</v>
+        <v>0.4112082719802856</v>
       </c>
       <c r="M2" t="n">
-        <v>3.233272764191497e-06</v>
+        <v>0.7372314929962158</v>
       </c>
       <c r="N2" t="n">
-        <v>1.281075856240932e-05</v>
+        <v>0.2883411347866058</v>
       </c>
       <c r="O2" t="n">
-        <v>8.277977030957118e-06</v>
+        <v>0.1999444514513016</v>
       </c>
       <c r="P2" t="n">
-        <v>4.975278898200486e-06</v>
+        <v>0.2950681746006012</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.269125151447952e-06</v>
+        <v>0.248417004942894</v>
       </c>
       <c r="R2" t="n">
-        <v>4.219052698317682e-06</v>
+        <v>0.1919021606445312</v>
       </c>
       <c r="S2" t="n">
-        <v>3.157996388836182e-07</v>
+        <v>0.09710507839918137</v>
       </c>
       <c r="T2" t="n">
-        <v>4.471872216527117e-06</v>
+        <v>0.3082647919654846</v>
       </c>
       <c r="U2" t="n">
-        <v>2.796202124955016e-06</v>
+        <v>0.05102438479661942</v>
       </c>
       <c r="V2" t="n">
-        <v>5.631076874124119e-06</v>
+        <v>0.1041212230920792</v>
       </c>
       <c r="W2" t="n">
-        <v>2.308380317117553e-06</v>
+        <v>0.009991761296987534</v>
       </c>
       <c r="X2" t="n">
-        <v>9.250752555090003e-06</v>
+        <v>0.06378540396690369</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.948353423766093e-06</v>
+        <v>0.05503768101334572</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.096053892979398e-06</v>
+        <v>0.0896017923951149</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.756337383085338e-06</v>
+        <v>0.08906838297843933</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.598485924769193e-06</v>
+        <v>0.05118216574192047</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.411364771949593e-07</v>
+        <v>0.2191071212291718</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.670090796324075e-06</v>
+        <v>0.06674312800168991</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.602638803888112e-06</v>
+        <v>0.1360704600811005</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.373561758555297e-06</v>
+        <v>0.2928264737129211</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.90834407476359e-06</v>
+        <v>0.1354846805334091</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.906881834656815e-06</v>
+        <v>0.04911043494939804</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.469834256175091e-07</v>
+        <v>0.03074763715267181</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.623006023190101e-06</v>
+        <v>0.1453150063753128</v>
       </c>
       <c r="AK2" t="n">
-        <v>6.363881766446866e-06</v>
+        <v>0.1292612999677658</v>
       </c>
       <c r="AL2" t="n">
-        <v>8.933135177358054e-06</v>
+        <v>0.1721135973930359</v>
       </c>
       <c r="AM2" t="n">
-        <v>6.22418610873865e-06</v>
+        <v>0.02141666412353516</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.214675416529644e-06</v>
+        <v>0.03540434688329697</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.97811527363956e-06</v>
+        <v>0.03265710175037384</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.25977032641822e-06</v>
+        <v>0.1526890099048615</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.030203631875338e-06</v>
+        <v>0.06972512602806091</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.318820745334961e-06</v>
+        <v>0.0572827011346817</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.444698439940112e-06</v>
+        <v>0.008438233286142349</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.39216660954844e-06</v>
+        <v>0.2562932968139648</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.868571861356031e-06</v>
+        <v>0.3279214799404144</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.389701264997711e-05</v>
+        <v>0.07182186096906662</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.697473276697565e-06</v>
+        <v>0.3542132973670959</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.275327278766781e-05</v>
+        <v>0.3399472534656525</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.021736342314398e-06</v>
+        <v>0.009549770504236221</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.780695129127707e-07</v>
+        <v>0.02640443667769432</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.272282800840912e-06</v>
+        <v>0.08636663854122162</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.635403006934212e-06</v>
+        <v>0.1170639544725418</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.011930054228287e-06</v>
+        <v>0.3616254925727844</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.003292618406704e-05</v>
+        <v>0.1777246445417404</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.912806328618899e-05</v>
+        <v>0.238176092505455</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.246605491673108e-06</v>
+        <v>0.1042781248688698</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.156306643679272e-05</v>
+        <v>0.1722853034734726</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.357141283937381e-06</v>
+        <v>0.3369271755218506</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.682960257516243e-06</v>
+        <v>0.2410421222448349</v>
       </c>
       <c r="BJ2" t="n">
-        <v>4.474430625123205e-06</v>
+        <v>0.1823147684335709</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.13361065814388e-05</v>
+        <v>0.003704000264406204</v>
       </c>
       <c r="BL2" t="n">
-        <v>4.929792339680716e-06</v>
+        <v>0.03075287491083145</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.212456845678389e-05</v>
+        <v>0.01690563559532166</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.718417843221687e-05</v>
+        <v>0.23794025182724</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.496690396787017e-06</v>
+        <v>0.232212245464325</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.393264579353854e-06</v>
+        <v>0.3053913414478302</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.337303092441289e-05</v>
+        <v>0.1433289796113968</v>
       </c>
       <c r="BR2" t="n">
-        <v>2.020046622419613e-06</v>
+        <v>0.01230718195438385</v>
       </c>
       <c r="BS2" t="n">
-        <v>3.964439656556351e-06</v>
+        <v>0.08037369698286057</v>
       </c>
       <c r="BT2" t="n">
-        <v>3.91278626921121e-06</v>
+        <v>0.1173684597015381</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.699270903074648e-06</v>
+        <v>0.07322042435407639</v>
       </c>
       <c r="BV2" t="n">
-        <v>3.414171260374133e-06</v>
+        <v>0.1390946358442307</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.072995923503186e-06</v>
+        <v>0.07939872145652771</v>
       </c>
       <c r="BX2" t="n">
-        <v>6.811868047407188e-07</v>
+        <v>0.2357233762741089</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.413026529917261e-05</v>
+        <v>0.2778895795345306</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.96497546514729e-07</v>
+        <v>0.02694853954017162</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.090343504183693e-06</v>
+        <v>0.02890132740139961</v>
       </c>
       <c r="CB2" t="n">
-        <v>7.280505997186992e-06</v>
+        <v>0.07429812848567963</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.523302555346163e-06</v>
+        <v>0.0729447677731514</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.361897031732951e-06</v>
+        <v>0.1969776302576065</v>
       </c>
       <c r="CE2" t="n">
-        <v>7.170495791797293e-06</v>
+        <v>0.0306263342499733</v>
       </c>
       <c r="CF2" t="n">
-        <v>9.997046390708419e-07</v>
+        <v>0.1236953288316727</v>
       </c>
       <c r="CG2" t="n">
-        <v>1.169775373455195e-06</v>
+        <v>0.2309425473213196</v>
       </c>
       <c r="CH2" t="n">
-        <v>2.46153945226979e-06</v>
+        <v>0.03123797476291656</v>
       </c>
       <c r="CI2" t="n">
-        <v>4.083190560777439e-06</v>
+        <v>0.1869398206472397</v>
       </c>
       <c r="CJ2" t="n">
-        <v>9.28161909996561e-07</v>
+        <v>0.03225076943635941</v>
       </c>
       <c r="CK2" t="n">
-        <v>2.103060523950262e-06</v>
+        <v>0.04405612125992775</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.904479404402082e-06</v>
+        <v>0.005403192713856697</v>
       </c>
       <c r="CM2" t="n">
-        <v>5.947803401795682e-06</v>
+        <v>0.008610321208834648</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.418925305391895e-06</v>
+        <v>0.5247535109519958</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.192038234876236e-05</v>
+        <v>0.2352673709392548</v>
       </c>
       <c r="CP2" t="n">
-        <v>6.897892035340192e-06</v>
+        <v>0.4842903017997742</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.023254637606442e-06</v>
+        <v>0.05518310517072678</v>
       </c>
       <c r="CR2" t="n">
-        <v>5.737709216191433e-06</v>
+        <v>0.1799081414937973</v>
       </c>
       <c r="CS2" t="n">
-        <v>4.717839146906044e-06</v>
+        <v>0.0447789803147316</v>
       </c>
       <c r="CT2" t="n">
-        <v>1.504556803411106e-05</v>
+        <v>0.0515679344534874</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.124957270803861e-05</v>
+        <v>0.1129237785935402</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.353537411181605e-06</v>
+        <v>0.1907719224691391</v>
       </c>
       <c r="CW2" t="n">
-        <v>5.548611625272315e-06</v>
+        <v>0.04996529221534729</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.184944267151877e-06</v>
+        <v>0.1194090247154236</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.135279262598488e-06</v>
+        <v>0.2346744984388351</v>
       </c>
       <c r="CZ2" t="n">
-        <v>3.655740556496312e-06</v>
+        <v>0.08206287026405334</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.841545440584014e-06</v>
+        <v>0.1403378397226334</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.469065182391205e-06</v>
+        <v>0.06292930990457535</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.197920482809423e-06</v>
+        <v>0.03133740276098251</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.500522209127666e-06</v>
+        <v>0.01167295966297388</v>
       </c>
       <c r="DE2" t="n">
-        <v>6.275039595493581e-06</v>
+        <v>0.1579272300004959</v>
       </c>
       <c r="DF2" t="n">
-        <v>9.593251888873056e-06</v>
+        <v>0.01730743795633316</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.173029861296527e-05</v>
+        <v>0.2859198451042175</v>
       </c>
       <c r="DH2" t="n">
-        <v>4.21112054027617e-06</v>
+        <v>0.06003376841545105</v>
       </c>
       <c r="DI2" t="n">
-        <v>7.136809472285677e-06</v>
+        <v>0.04356018453836441</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.786234401559341e-06</v>
+        <v>0.06363162398338318</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.400138550408883e-06</v>
+        <v>0.203368678689003</v>
       </c>
       <c r="DL2" t="n">
-        <v>3.296104114269838e-05</v>
+        <v>0.07769203931093216</v>
       </c>
       <c r="DM2" t="n">
-        <v>1.53995042637689e-05</v>
+        <v>0.0807369127869606</v>
       </c>
       <c r="DN2" t="n">
-        <v>4.300485215935623e-06</v>
+        <v>0.06237912178039551</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.026105474011274e-05</v>
+        <v>0.01240904442965984</v>
       </c>
       <c r="DP2" t="n">
-        <v>4.159239779255586e-06</v>
+        <v>0.02538271993398666</v>
       </c>
       <c r="DQ2" t="n">
-        <v>3.063953727178159e-06</v>
+        <v>0.05615556985139847</v>
       </c>
       <c r="DR2" t="n">
-        <v>3.200291303073755e-06</v>
+        <v>0.2973213195800781</v>
       </c>
       <c r="DS2" t="n">
-        <v>2.059626240225043e-06</v>
+        <v>0.02631782926619053</v>
       </c>
       <c r="DT2" t="n">
-        <v>7.562633186353196e-08</v>
+        <v>0.05217133089900017</v>
       </c>
       <c r="DU2" t="n">
-        <v>1.81280086053448e-06</v>
+        <v>0.1340629011392593</v>
       </c>
       <c r="DV2" t="n">
-        <v>7.85293013905175e-06</v>
+        <v>0.2785214781761169</v>
       </c>
       <c r="DW2" t="n">
-        <v>4.129719854972791e-06</v>
+        <v>0.05604345351457596</v>
       </c>
       <c r="DX2" t="n">
-        <v>6.067625690775458e-06</v>
+        <v>0.3128179311752319</v>
       </c>
       <c r="DY2" t="n">
-        <v>2.442816594339092e-06</v>
+        <v>0.179875373840332</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.511343488251441e-07</v>
+        <v>0.1428856253623962</v>
       </c>
       <c r="EA2" t="n">
-        <v>5.411329766502604e-06</v>
+        <v>0.07773967087268829</v>
       </c>
       <c r="EB2" t="n">
-        <v>3.354069349370548e-06</v>
+        <v>0.08143894374370575</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.013497351072147e-06</v>
+        <v>0.05148972943425179</v>
       </c>
       <c r="ED2" t="n">
-        <v>1.715204234642442e-06</v>
+        <v>0.05987904220819473</v>
       </c>
       <c r="EE2" t="n">
-        <v>1.047143814503215e-05</v>
+        <v>0.1590850651264191</v>
       </c>
       <c r="EF2" t="n">
-        <v>1.13233716092509e-06</v>
+        <v>0.3281890749931335</v>
       </c>
       <c r="EG2" t="n">
-        <v>2.174746259697713e-05</v>
+        <v>0.02297525107860565</v>
       </c>
       <c r="EH2" t="n">
-        <v>8.995582447823836e-07</v>
+        <v>0.2036287933588028</v>
       </c>
       <c r="EI2" t="n">
-        <v>8.216797141358256e-06</v>
+        <v>0.2636590301990509</v>
       </c>
       <c r="EJ2" t="n">
-        <v>5.937623882346088e-06</v>
+        <v>0.04271293431520462</v>
       </c>
       <c r="EK2" t="n">
-        <v>1.151511878560996e-05</v>
+        <v>0.2559339106082916</v>
       </c>
       <c r="EL2" t="n">
-        <v>6.157765142233984e-07</v>
+        <v>0.005138367414474487</v>
       </c>
       <c r="EM2" t="n">
-        <v>1.645770339564478e-06</v>
+        <v>0.1181426793336868</v>
       </c>
       <c r="EN2" t="n">
-        <v>3.192750227754004e-06</v>
+        <v>0.01580885052680969</v>
       </c>
       <c r="EO2" t="n">
-        <v>4.773246928380104e-06</v>
+        <v>0.09230320155620575</v>
       </c>
       <c r="EP2" t="n">
-        <v>4.591925971908495e-06</v>
+        <v>0.1083674430847168</v>
       </c>
       <c r="EQ2" t="n">
-        <v>3.820429355982924e-06</v>
+        <v>0.140614852309227</v>
       </c>
       <c r="ER2" t="n">
-        <v>2.113952405125019e-06</v>
+        <v>0.2712473571300507</v>
       </c>
       <c r="ES2" t="n">
-        <v>6.637851583946031e-06</v>
+        <v>0.1097685173153877</v>
       </c>
       <c r="ET2" t="n">
-        <v>2.094894000492786e-07</v>
+        <v>0.190390557050705</v>
       </c>
       <c r="EU2" t="n">
-        <v>4.145432740187971e-06</v>
+        <v>0.08779741823673248</v>
       </c>
       <c r="EV2" t="n">
-        <v>3.189004246451077e-06</v>
+        <v>0.09117025136947632</v>
       </c>
       <c r="EW2" t="n">
-        <v>9.275540264752635e-07</v>
+        <v>0.007668696343898773</v>
       </c>
       <c r="EX2" t="n">
-        <v>3.065509645239217e-06</v>
+        <v>0.1899804025888443</v>
       </c>
       <c r="EY2" t="n">
-        <v>4.644508862838848e-06</v>
+        <v>0.06025911122560501</v>
       </c>
       <c r="EZ2" t="n">
-        <v>3.66816925634339e-06</v>
+        <v>0.1252197623252869</v>
       </c>
       <c r="FA2" t="n">
-        <v>9.968528047465952e-07</v>
+        <v>0.2208542972803116</v>
       </c>
       <c r="FB2" t="n">
-        <v>2.452061380608939e-06</v>
+        <v>0.08123082667589188</v>
       </c>
       <c r="FC2" t="n">
-        <v>4.167784027231392e-06</v>
+        <v>0.1248749122023582</v>
       </c>
       <c r="FD2" t="n">
-        <v>8.698018518771278e-07</v>
+        <v>0.0385163240134716</v>
       </c>
       <c r="FE2" t="n">
-        <v>2.816061623889254e-06</v>
+        <v>0.007431170903146267</v>
       </c>
       <c r="FF2" t="n">
-        <v>1.605383545211225e-06</v>
+        <v>0.01534824911504984</v>
       </c>
       <c r="FG2" t="n">
-        <v>2.224504441983299e-06</v>
+        <v>0.1558139026165009</v>
       </c>
       <c r="FH2" t="n">
-        <v>5.317203886079369e-06</v>
+        <v>0.1672181487083435</v>
       </c>
       <c r="FI2" t="n">
-        <v>5.19670311405207e-06</v>
+        <v>0.155434250831604</v>
       </c>
       <c r="FJ2" t="n">
-        <v>5.652588583870966e-07</v>
+        <v>0.2544066309928894</v>
       </c>
       <c r="FK2" t="n">
-        <v>1.304621832787234e-06</v>
+        <v>0.08263906091451645</v>
       </c>
       <c r="FL2" t="n">
-        <v>3.875667289321427e-07</v>
+        <v>0.05534856393933296</v>
       </c>
       <c r="FM2" t="n">
-        <v>1.023592290039232e-06</v>
+        <v>0.1021610498428345</v>
       </c>
       <c r="FN2" t="n">
-        <v>5.141699148225598e-06</v>
+        <v>0.2703814208507538</v>
       </c>
       <c r="FO2" t="n">
-        <v>1.170223981716845e-06</v>
+        <v>0.1281501948833466</v>
       </c>
       <c r="FP2" t="n">
-        <v>4.651678864320274e-06</v>
+        <v>0.01368210092186928</v>
       </c>
       <c r="FQ2" t="n">
-        <v>5.862507350684609e-06</v>
+        <v>0.2456739097833633</v>
       </c>
       <c r="FR2" t="n">
-        <v>1.475116187066305e-05</v>
+        <v>0.2613829076290131</v>
       </c>
       <c r="FS2" t="n">
-        <v>6.321605269477004e-06</v>
+        <v>0.01948616653680801</v>
       </c>
       <c r="FT2" t="n">
-        <v>1.938642890308984e-05</v>
+        <v>0.3995410799980164</v>
       </c>
       <c r="FU2" t="n">
-        <v>2.343317362374364e-07</v>
+        <v>0.4159896373748779</v>
       </c>
       <c r="FV2" t="n">
-        <v>1.347190845990553e-06</v>
+        <v>0.1679328680038452</v>
       </c>
       <c r="FW2" t="n">
-        <v>1.080088713933947e-05</v>
+        <v>0.002318588085472584</v>
       </c>
       <c r="FX2" t="n">
-        <v>7.162967904150719e-06</v>
+        <v>0.06489229202270508</v>
       </c>
       <c r="FY2" t="n">
-        <v>3.888089850079268e-06</v>
+        <v>0.1246260777115822</v>
       </c>
       <c r="FZ2" t="n">
-        <v>1.192473064293154e-05</v>
+        <v>0.549591064453125</v>
       </c>
       <c r="GA2" t="n">
-        <v>6.481269792857347e-06</v>
+        <v>0.006850026547908783</v>
       </c>
       <c r="GB2" t="n">
-        <v>7.856387128413189e-06</v>
+        <v>0.05031502246856689</v>
       </c>
       <c r="GC2" t="n">
-        <v>1.069986637958209e-06</v>
+        <v>0.2122145742177963</v>
       </c>
       <c r="GD2" t="n">
-        <v>2.553022932261229e-05</v>
+        <v>0.4718365371227264</v>
       </c>
       <c r="GE2" t="n">
-        <v>6.098370022300514e-07</v>
+        <v>0.1235788464546204</v>
       </c>
       <c r="GF2" t="n">
-        <v>4.407216351864918e-07</v>
+        <v>0.03069783560931683</v>
       </c>
       <c r="GG2" t="n">
-        <v>6.240091352083255e-06</v>
+        <v>0.08357366174459457</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2.122879076913169e-15</v>
+        <v>0.006444637663662434</v>
       </c>
       <c r="B3" t="n">
-        <v>1.387370510900869e-15</v>
+        <v>0.003366913413628936</v>
       </c>
       <c r="C3" t="n">
-        <v>3.400847871137857e-16</v>
+        <v>0.004754823632538319</v>
       </c>
       <c r="D3" t="n">
-        <v>1.026487295635375e-14</v>
+        <v>0.003216833109036088</v>
       </c>
       <c r="E3" t="n">
-        <v>2.729492945275887e-15</v>
+        <v>0.001722929533571005</v>
       </c>
       <c r="F3" t="n">
-        <v>1.126901780982952e-14</v>
+        <v>0.007669011596590281</v>
       </c>
       <c r="G3" t="n">
-        <v>2.082048488965486e-15</v>
+        <v>0.001290599931962788</v>
       </c>
       <c r="H3" t="n">
-        <v>1.440736339434969e-15</v>
+        <v>0.002524565905332565</v>
       </c>
       <c r="I3" t="n">
-        <v>1.017242735697394e-15</v>
+        <v>0.001214238116517663</v>
       </c>
       <c r="J3" t="n">
-        <v>2.216907569113158e-15</v>
+        <v>0.0086367167532444</v>
       </c>
       <c r="K3" t="n">
-        <v>6.600279777748113e-16</v>
+        <v>0.002906435169279575</v>
       </c>
       <c r="L3" t="n">
-        <v>2.358948853378837e-15</v>
+        <v>0.00544602470472455</v>
       </c>
       <c r="M3" t="n">
-        <v>6.53609839726876e-15</v>
+        <v>0.003864977275952697</v>
       </c>
       <c r="N3" t="n">
-        <v>1.194284903651278e-15</v>
+        <v>0.0009485059417784214</v>
       </c>
       <c r="O3" t="n">
-        <v>7.815380727836403e-15</v>
+        <v>0.01013530138880014</v>
       </c>
       <c r="P3" t="n">
-        <v>1.149260867339976e-15</v>
+        <v>1.156586222350597e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.896013905233689e-15</v>
+        <v>0.004375947173684835</v>
       </c>
       <c r="R3" t="n">
-        <v>1.133772340503839e-15</v>
+        <v>0.003587442915886641</v>
       </c>
       <c r="S3" t="n">
-        <v>6.590002091724366e-16</v>
+        <v>0.0005662246840074658</v>
       </c>
       <c r="T3" t="n">
-        <v>4.700500073537544e-15</v>
+        <v>0.002551143523305655</v>
       </c>
       <c r="U3" t="n">
-        <v>8.928391126132736e-16</v>
+        <v>0.001520241610705853</v>
       </c>
       <c r="V3" t="n">
-        <v>3.105670123909534e-16</v>
+        <v>0.0007055838941596448</v>
       </c>
       <c r="W3" t="n">
-        <v>3.220532132601072e-15</v>
+        <v>0.0002531010832171887</v>
       </c>
       <c r="X3" t="n">
-        <v>5.613075583217435e-16</v>
+        <v>0.001323054078966379</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.312640937760215e-17</v>
+        <v>0.0008304304210469127</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.188219830111582e-15</v>
+        <v>0.001073635881766677</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.177876210417018e-16</v>
+        <v>0.0009463527239859104</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.987628473923097e-16</v>
+        <v>0.003310727886855602</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.276219911966794e-16</v>
+        <v>0.001917954534292221</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.051674752647362e-16</v>
+        <v>3.034383553313091e-05</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.591626365142376e-15</v>
+        <v>0.001202636631205678</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.648974413198873e-15</v>
+        <v>5.896398215554655e-05</v>
       </c>
       <c r="AG3" t="n">
-        <v>4.698261471337069e-16</v>
+        <v>0.002288379007950425</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.259859018054154e-15</v>
+        <v>0.0002494583604857326</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.256466651100401e-15</v>
+        <v>0.0003510958049446344</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.068039940446439e-16</v>
+        <v>0.002746905665844679</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.917170137650647e-15</v>
+        <v>0.0003440015716478229</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.167738153557993e-15</v>
+        <v>0.001773592550307512</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.703900370542697e-15</v>
+        <v>7.405225187540054e-05</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.209752439952191e-16</v>
+        <v>0.002478961134329438</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.524777466153883e-15</v>
+        <v>0.001501343911513686</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.151668558492546e-15</v>
+        <v>0.002079934813082218</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.347660886944721e-16</v>
+        <v>0.0005463061388581991</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.464449672950544e-16</v>
+        <v>0.0008382784435525537</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.057891875856078e-16</v>
+        <v>0.0002731462591327727</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.570108128392091e-15</v>
+        <v>0.005435819737613201</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.437853470053976e-15</v>
+        <v>0.003364794421941042</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.030923062576874e-15</v>
+        <v>0.0005390053847804666</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.536735891813194e-15</v>
+        <v>0.00017730169929564</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.203850351727984e-15</v>
+        <v>0.002800439950078726</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.485433326031994e-15</v>
+        <v>0.01014602836221457</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.317938002604572e-16</v>
+        <v>0.002265868009999394</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.811335506611059e-16</v>
+        <v>0.003255649702623487</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.239480570013518e-15</v>
+        <v>0.0004238973488099873</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.788207684620273e-16</v>
+        <v>0.00267768488265574</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.176256457153656e-15</v>
+        <v>0.004835566971451044</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.500140034202827e-16</v>
+        <v>0.001419949112460017</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.746537270760375e-16</v>
+        <v>0.001545729348435998</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.697424496906064e-15</v>
+        <v>0.002335353987291455</v>
       </c>
       <c r="BH3" t="n">
-        <v>1.741403283677973e-15</v>
+        <v>0.002960428595542908</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.902615570517976e-15</v>
+        <v>0.001648712204769254</v>
       </c>
       <c r="BJ3" t="n">
-        <v>3.270714228984238e-16</v>
+        <v>0.000265647511696443</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.91957096479799e-18</v>
+        <v>0.001295147929340601</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.325548540696093e-15</v>
+        <v>0.002007617149502039</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.499390727681862e-15</v>
+        <v>0.001790195005014539</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.567261469669594e-15</v>
+        <v>0.003056026063859463</v>
       </c>
       <c r="BO3" t="n">
-        <v>8.889735718793602e-16</v>
+        <v>0.002021561842411757</v>
       </c>
       <c r="BP3" t="n">
-        <v>1.113490560098308e-15</v>
+        <v>0.001010499661788344</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.88457996629738e-16</v>
+        <v>0.0008306216332130134</v>
       </c>
       <c r="BR3" t="n">
-        <v>1.017044424108618e-15</v>
+        <v>0.002854825230315328</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.117838247867667e-16</v>
+        <v>0.001209961017593741</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.74079438737799e-16</v>
+        <v>0.001364692696370184</v>
       </c>
       <c r="BU3" t="n">
-        <v>2.4276658835325e-15</v>
+        <v>0.002775056520476937</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.612525011801719e-17</v>
+        <v>0.0005419209483079612</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.689130572927267e-16</v>
+        <v>0.00134564156178385</v>
       </c>
       <c r="BX3" t="n">
-        <v>2.922358959233902e-15</v>
+        <v>0.002609628485515714</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.236357895311815e-16</v>
+        <v>0.001010652631521225</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.681384226728921e-15</v>
+        <v>0.00584261491894722</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.903122760515095e-17</v>
+        <v>0.0002422253892291337</v>
       </c>
       <c r="CB3" t="n">
-        <v>2.113620583283206e-15</v>
+        <v>0.002232196740806103</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.004311824845492e-15</v>
+        <v>0.0001546968705952168</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.865899184041279e-16</v>
+        <v>0.001883018761873245</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.370961894525777e-15</v>
+        <v>0.002252080012112856</v>
       </c>
       <c r="CF3" t="n">
-        <v>1.069889433259275e-15</v>
+        <v>0.00136115588247776</v>
       </c>
       <c r="CG3" t="n">
-        <v>1.765936851841365e-15</v>
+        <v>0.0002056552330031991</v>
       </c>
       <c r="CH3" t="n">
-        <v>4.881812981611484e-16</v>
+        <v>0.0008353945449925959</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.86344728472928e-15</v>
+        <v>0.002149869920685887</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.009961719892135e-16</v>
+        <v>0.0005074156797491014</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.223197420393738e-15</v>
+        <v>0.000141795098898001</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.207261766040569e-16</v>
+        <v>4.271129728294909e-05</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.244554195115947e-16</v>
+        <v>0.001337219262495637</v>
       </c>
       <c r="CN3" t="n">
-        <v>4.530890196179343e-15</v>
+        <v>0.003053412074223161</v>
       </c>
       <c r="CO3" t="n">
-        <v>7.143441772757301e-17</v>
+        <v>0.001067314529791474</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.863706265052903e-15</v>
+        <v>0.0005570441135205328</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.484492265172607e-15</v>
+        <v>0.0004845581715926528</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.633295515707841e-15</v>
+        <v>0.002427065512165427</v>
       </c>
       <c r="CS3" t="n">
-        <v>9.207858000376268e-16</v>
+        <v>0.003257907228544354</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.471330964986545e-15</v>
+        <v>0.001004087156616151</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.926755797756487e-15</v>
+        <v>0.0006551722763106227</v>
       </c>
       <c r="CV3" t="n">
-        <v>5.080555233701517e-17</v>
+        <v>0.002242288552224636</v>
       </c>
       <c r="CW3" t="n">
-        <v>9.699159344398627e-16</v>
+        <v>0.00239028874784708</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.269656648155044e-15</v>
+        <v>0.0009001962607726455</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.801859307376183e-15</v>
+        <v>0.0002363720996072516</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.345171541226897e-15</v>
+        <v>0.0002136977855116129</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.088747460787083e-15</v>
+        <v>0.002056399593129754</v>
       </c>
       <c r="DB3" t="n">
-        <v>4.045741964183634e-16</v>
+        <v>0.0001925046817632392</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.236800875405761e-15</v>
+        <v>0.0004232807550579309</v>
       </c>
       <c r="DD3" t="n">
-        <v>8.324251229250711e-16</v>
+        <v>0.0003251419111620635</v>
       </c>
       <c r="DE3" t="n">
-        <v>2.286943006049222e-15</v>
+        <v>0.002770032966509461</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.962317629014012e-15</v>
+        <v>0.0007629441097378731</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.314383383156848e-15</v>
+        <v>0.001665468793362379</v>
       </c>
       <c r="DH3" t="n">
-        <v>8.908475263960419e-16</v>
+        <v>0.0009148975368589163</v>
       </c>
       <c r="DI3" t="n">
-        <v>4.857644167011003e-15</v>
+        <v>0.0002085411688312888</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.054748828833716e-15</v>
+        <v>0.002227504272013903</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.686119776178783e-15</v>
+        <v>0.0004317779093980789</v>
       </c>
       <c r="DL3" t="n">
-        <v>3.126518886994133e-15</v>
+        <v>0.0004547472635749727</v>
       </c>
       <c r="DM3" t="n">
-        <v>2.725746518550181e-15</v>
+        <v>0.003238719888031483</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.538831966210318e-15</v>
+        <v>0.000529589771758765</v>
       </c>
       <c r="DO3" t="n">
-        <v>5.445375765155292e-16</v>
+        <v>0.0009572479757480323</v>
       </c>
       <c r="DP3" t="n">
-        <v>2.046014436839867e-15</v>
+        <v>0.000425543898018077</v>
       </c>
       <c r="DQ3" t="n">
-        <v>4.476384367177357e-16</v>
+        <v>0.0003071399696636945</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.028265507587345e-16</v>
+        <v>0.0001884069351945072</v>
       </c>
       <c r="DS3" t="n">
-        <v>6.706084251376424e-17</v>
+        <v>0.0009399261325597763</v>
       </c>
       <c r="DT3" t="n">
-        <v>1.076540230081997e-15</v>
+        <v>7.866896339692175e-05</v>
       </c>
       <c r="DU3" t="n">
-        <v>5.91437049651171e-16</v>
+        <v>0.001700094086118042</v>
       </c>
       <c r="DV3" t="n">
-        <v>5.418027718266411e-16</v>
+        <v>0.00154274539090693</v>
       </c>
       <c r="DW3" t="n">
-        <v>3.140438179416363e-16</v>
+        <v>0.0012021753937006</v>
       </c>
       <c r="DX3" t="n">
-        <v>1.812422231744918e-15</v>
+        <v>0.0004380089812912047</v>
       </c>
       <c r="DY3" t="n">
-        <v>1.047625489878051e-15</v>
+        <v>0.001026156940497458</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.245788106734366e-15</v>
+        <v>0.003636946436017752</v>
       </c>
       <c r="EA3" t="n">
-        <v>1.549721951175811e-15</v>
+        <v>0.0009978777961805463</v>
       </c>
       <c r="EB3" t="n">
-        <v>2.488687831118594e-15</v>
+        <v>0.0006892779492773116</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.863640831757728e-15</v>
+        <v>0.0001808875531423837</v>
       </c>
       <c r="ED3" t="n">
-        <v>1.684179855343841e-15</v>
+        <v>0.0002512946375645697</v>
       </c>
       <c r="EE3" t="n">
-        <v>1.433431315539611e-15</v>
+        <v>3.680505324155092e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>7.065254278978625e-16</v>
+        <v>0.0003308461746200919</v>
       </c>
       <c r="EG3" t="n">
-        <v>9.472305921673797e-17</v>
+        <v>0.0009634668822400272</v>
       </c>
       <c r="EH3" t="n">
-        <v>1.510128243089356e-15</v>
+        <v>0.001809524837881327</v>
       </c>
       <c r="EI3" t="n">
-        <v>3.763246682455873e-15</v>
+        <v>1.04337086668238e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>6.780658620239468e-16</v>
+        <v>0.0003882128221448511</v>
       </c>
       <c r="EK3" t="n">
-        <v>1.043880227822648e-15</v>
+        <v>0.0006786967278458178</v>
       </c>
       <c r="EL3" t="n">
-        <v>1.711120373505974e-16</v>
+        <v>0.0001866442617028952</v>
       </c>
       <c r="EM3" t="n">
-        <v>5.974943410756641e-16</v>
+        <v>2.077201133943163e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>1.9999961625195e-17</v>
+        <v>0.0002812175080180168</v>
       </c>
       <c r="EO3" t="n">
-        <v>1.350032451552952e-15</v>
+        <v>0.002200608374550939</v>
       </c>
       <c r="EP3" t="n">
-        <v>3.205189613069218e-16</v>
+        <v>0.002693479182198644</v>
       </c>
       <c r="EQ3" t="n">
-        <v>5.08032574071237e-15</v>
+        <v>0.0008148011984303594</v>
       </c>
       <c r="ER3" t="n">
-        <v>7.227148744978523e-16</v>
+        <v>0.0009849362540990114</v>
       </c>
       <c r="ES3" t="n">
-        <v>2.531994084612865e-15</v>
+        <v>0.0003326989826746285</v>
       </c>
       <c r="ET3" t="n">
-        <v>1.538916140109451e-15</v>
+        <v>0.0010809525847435</v>
       </c>
       <c r="EU3" t="n">
-        <v>9.282931192235906e-17</v>
+        <v>0.0003078233567066491</v>
       </c>
       <c r="EV3" t="n">
-        <v>2.482794387629835e-15</v>
+        <v>1.112712197937071e-06</v>
       </c>
       <c r="EW3" t="n">
-        <v>1.285325063613355e-15</v>
+        <v>0.0002932544448412955</v>
       </c>
       <c r="EX3" t="n">
-        <v>9.134783144527659e-17</v>
+        <v>0.002173445420339704</v>
       </c>
       <c r="EY3" t="n">
-        <v>3.641163294372518e-16</v>
+        <v>0.001737446058541536</v>
       </c>
       <c r="EZ3" t="n">
-        <v>1.749284501735701e-15</v>
+        <v>0.001090124482288957</v>
       </c>
       <c r="FA3" t="n">
-        <v>1.755174662971789e-15</v>
+        <v>0.0007115353946574032</v>
       </c>
       <c r="FB3" t="n">
-        <v>1.351321741577792e-15</v>
+        <v>0.0005808544810861349</v>
       </c>
       <c r="FC3" t="n">
-        <v>2.117002997599829e-15</v>
+        <v>0.002455742796882987</v>
       </c>
       <c r="FD3" t="n">
-        <v>1.641743345867722e-16</v>
+        <v>0.0005538703990168869</v>
       </c>
       <c r="FE3" t="n">
-        <v>1.420541591664768e-15</v>
+        <v>0.0001029788254527375</v>
       </c>
       <c r="FF3" t="n">
-        <v>5.107966013968054e-16</v>
+        <v>0.0004275237151887268</v>
       </c>
       <c r="FG3" t="n">
-        <v>1.570064506195307e-16</v>
+        <v>0.002797082299366593</v>
       </c>
       <c r="FH3" t="n">
-        <v>3.246678557375154e-15</v>
+        <v>0.0003070530947297812</v>
       </c>
       <c r="FI3" t="n">
-        <v>1.813718403912454e-15</v>
+        <v>0.0006357365055009723</v>
       </c>
       <c r="FJ3" t="n">
-        <v>2.617399635826017e-17</v>
+        <v>0.002050586743280292</v>
       </c>
       <c r="FK3" t="n">
-        <v>1.275988642952244e-15</v>
+        <v>0.0004972427850589156</v>
       </c>
       <c r="FL3" t="n">
-        <v>7.155671869724469e-16</v>
+        <v>0.002387391403317451</v>
       </c>
       <c r="FM3" t="n">
-        <v>1.053602895507706e-15</v>
+        <v>0.0001825478684622794</v>
       </c>
       <c r="FN3" t="n">
-        <v>1.258567504567828e-15</v>
+        <v>0.001618558191694319</v>
       </c>
       <c r="FO3" t="n">
-        <v>2.309321828273918e-15</v>
+        <v>0.001080815447494388</v>
       </c>
       <c r="FP3" t="n">
-        <v>8.375355903332115e-16</v>
+        <v>0.0027839126996696</v>
       </c>
       <c r="FQ3" t="n">
-        <v>1.500956570336487e-15</v>
+        <v>0.007157199084758759</v>
       </c>
       <c r="FR3" t="n">
-        <v>2.218302208860812e-15</v>
+        <v>0.0007252080249600112</v>
       </c>
       <c r="FS3" t="n">
-        <v>1.661454914281073e-15</v>
+        <v>0.00276538822799921</v>
       </c>
       <c r="FT3" t="n">
-        <v>4.522906910651471e-15</v>
+        <v>0.004057019017636776</v>
       </c>
       <c r="FU3" t="n">
-        <v>1.554578891034927e-16</v>
+        <v>0.001953188329935074</v>
       </c>
       <c r="FV3" t="n">
-        <v>7.700890037213117e-16</v>
+        <v>0.002664190717041492</v>
       </c>
       <c r="FW3" t="n">
-        <v>1.089170444237625e-15</v>
+        <v>0.002272155834361911</v>
       </c>
       <c r="FX3" t="n">
-        <v>1.280315604884174e-15</v>
+        <v>0.002609006362035871</v>
       </c>
       <c r="FY3" t="n">
-        <v>6.991884814483049e-16</v>
+        <v>0.002413009759038687</v>
       </c>
       <c r="FZ3" t="n">
-        <v>3.331827179672603e-15</v>
+        <v>0.005699287168681622</v>
       </c>
       <c r="GA3" t="n">
-        <v>6.705984195609529e-16</v>
+        <v>0.0001535190967842937</v>
       </c>
       <c r="GB3" t="n">
-        <v>1.844924368238723e-15</v>
+        <v>0.00281619094312191</v>
       </c>
       <c r="GC3" t="n">
-        <v>4.329186240449676e-15</v>
+        <v>0.001830173190683126</v>
       </c>
       <c r="GD3" t="n">
-        <v>2.330448947560808e-15</v>
+        <v>0.001228814711794257</v>
       </c>
       <c r="GE3" t="n">
-        <v>4.445591013775519e-16</v>
+        <v>0.0001635391672607511</v>
       </c>
       <c r="GF3" t="n">
-        <v>3.51409194102102e-15</v>
+        <v>0.0002280092739965767</v>
       </c>
       <c r="GG3" t="n">
-        <v>1.132346572295373e-15</v>
+        <v>0.001116071827709675</v>
       </c>
     </row>
     <row r="4">
